--- a/data/trans_orig/Q02D_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q02D_R-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas diarias, a la semana, que dedica la persona entrevistada a cuidar a las personas del hogar que lo necesitan</t>
+          <t>Número medio de horas diarias, a la semana, que dedica la persona entrevistada a cuidar a las personas del hogar que lo necesitan (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,16</t>
+          <t>2,09; 4,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,24; 7,88</t>
+          <t>6,29; 7,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -736,42 +736,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 4,61</t>
+          <t>3,06; 4,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,23; 9,63</t>
+          <t>8,29; 9,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,78; 13,25</t>
+          <t>10,85; 13,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 10,39</t>
+          <t>4,2; 10,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,12</t>
+          <t>2,86; 4,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,69; 8,74</t>
+          <t>7,64; 8,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,26; 11,25</t>
+          <t>9,35; 11,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 14,85</t>
+          <t>4,78; 14,02</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 7,86</t>
+          <t>5,66; 7,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 7,71</t>
+          <t>6,56; 7,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,84; 14,25</t>
+          <t>10,9; 14,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -876,42 +876,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,23; 9,97</t>
+          <t>8,21; 9,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,67; 8,77</t>
+          <t>7,62; 8,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,05; 14,6</t>
+          <t>11,95; 14,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,52; 13,73</t>
+          <t>8,76; 13,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,57; 8,94</t>
+          <t>7,52; 8,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 8,23</t>
+          <t>7,43; 8,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,94; 14,1</t>
+          <t>11,97; 14,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,51; 14,33</t>
+          <t>9,35; 14,7</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,97</t>
+          <t>1,55; 3,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 3,82</t>
+          <t>2,59; 3,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,02; 10,68</t>
+          <t>8,04; 10,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,99; 20,4</t>
+          <t>10,11; 20,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,7</t>
+          <t>3,14; 4,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,26</t>
+          <t>4,22; 5,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,95; 13,1</t>
+          <t>9,93; 13,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,65; 15,24</t>
+          <t>8,44; 14,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 3,64</t>
+          <t>2,61; 3,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 4,47</t>
+          <t>3,64; 4,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,37; 11,59</t>
+          <t>9,34; 11,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,91; 16,09</t>
+          <t>9,9; 15,67</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,36</t>
+          <t>1,65; 2,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 8,34</t>
+          <t>5,42; 8,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,42 +1156,42 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 5,28</t>
+          <t>3,56; 5,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,69; 9,07</t>
+          <t>7,66; 9,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 9,34</t>
+          <t>7,38; 9,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,23; 14,33</t>
+          <t>10,22; 14,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 3,9</t>
+          <t>2,82; 3,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 7,98</t>
+          <t>6,91; 7,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,0; 8,59</t>
+          <t>6,94; 8,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,02; 12,78</t>
+          <t>9,0; 12,5</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 7,75</t>
+          <t>4,61; 8,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,22; 5,96</t>
+          <t>4,21; 6,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,91; 3,82</t>
+          <t>2,92; 3,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,63</t>
+          <t>2,96; 4,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,3; 10,62</t>
+          <t>7,28; 10,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,54; 7,1</t>
+          <t>5,56; 7,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 4,77</t>
+          <t>4,14; 4,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,11</t>
+          <t>3,72; 6,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,65; 9,15</t>
+          <t>6,62; 9,03</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,15; 6,42</t>
+          <t>5,23; 6,48</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 4,18</t>
+          <t>3,63; 4,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,4; 4,88</t>
+          <t>3,41; 4,84</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,34</t>
+          <t>1,65; 2,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,1; 2,88</t>
+          <t>2,05; 2,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,3; 7,42</t>
+          <t>5,3; 7,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,49; 15,04</t>
+          <t>10,37; 14,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,55</t>
+          <t>4,68; 7,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,14</t>
+          <t>3,91; 5,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,04</t>
+          <t>7,35; 10,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,58; 14,25</t>
+          <t>10,54; 14,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,21</t>
+          <t>3,29; 5,17</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,06</t>
+          <t>3,24; 4,04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,59; 8,37</t>
+          <t>6,58; 8,37</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,94; 13,72</t>
+          <t>11,02; 13,9</t>
         </is>
       </c>
     </row>
@@ -1556,17 +1556,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,19</t>
+          <t>2,58; 4,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,75; 3,43</t>
+          <t>2,77; 3,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,55; 11,3</t>
+          <t>8,67; 11,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1576,42 +1576,42 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,03; 5,51</t>
+          <t>4,09; 5,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 5,24</t>
+          <t>4,47; 5,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,02; 13,06</t>
+          <t>10,97; 13,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,63; 23,01</t>
+          <t>13,56; 22,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,72; 4,76</t>
+          <t>3,71; 4,76</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,84; 4,37</t>
+          <t>3,84; 4,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,34; 11,99</t>
+          <t>10,41; 12,03</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,02; 22,17</t>
+          <t>10,4; 22,14</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,7; 7,66</t>
+          <t>5,8; 7,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,32; 6,41</t>
+          <t>5,31; 6,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,89; 4,54</t>
+          <t>3,89; 4,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,49</t>
+          <t>3,71; 4,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,46; 10,28</t>
+          <t>8,46; 10,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,01; 7,85</t>
+          <t>7,03; 7,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,38; 6,2</t>
+          <t>5,4; 6,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,14</t>
+          <t>5,3; 6,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,54; 8,81</t>
+          <t>7,51; 8,85</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,51; 7,21</t>
+          <t>6,5; 7,2</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,87; 5,43</t>
+          <t>4,86; 5,43</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,76; 5,38</t>
+          <t>4,78; 5,4</t>
         </is>
       </c>
     </row>
@@ -1836,42 +1836,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,63; 4,33</t>
+          <t>3,65; 4,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,7; 5,16</t>
+          <t>4,68; 5,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,5; 7,33</t>
+          <t>6,5; 7,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,5; 7,34</t>
+          <t>5,48; 7,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,86; 6,55</t>
+          <t>5,87; 6,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,55; 6,97</t>
+          <t>6,55; 6,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,56; 9,36</t>
+          <t>8,59; 9,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,4; 8,58</t>
+          <t>7,41; 8,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,83; 8,4</t>
+          <t>7,84; 8,44</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,94</t>
+          <t>6,82; 7,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q02D_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q02D_R-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,05</t>
+          <t>9,5</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,99</t>
+          <t>6,0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,19</t>
+          <t>6,99</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,17</t>
+          <t>2,05; 4,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 7,91</t>
+          <t>6,26; 7,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,6; 9,45</t>
+          <t>6,78; 9,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 21,27</t>
+          <t>3,71; 21,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 4,74</t>
+          <t>3,04; 4,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,29; 9,65</t>
+          <t>8,31; 9,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,85; 13,19</t>
+          <t>10,82; 13,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,2; 10,89</t>
+          <t>4,76; 8,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 4,16</t>
+          <t>2,89; 4,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,64; 8,76</t>
+          <t>7,66; 8,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,35; 11,31</t>
+          <t>9,34; 11,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,78; 14,02</t>
+          <t>4,81; 12,0</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,03</t>
+          <t>12,43</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,17</t>
+          <t>11,39</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,87</t>
+          <t>11,59</t>
         </is>
       </c>
     </row>
@@ -856,47 +856,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 7,84</t>
+          <t>5,67; 7,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 7,67</t>
+          <t>6,62; 7,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,9; 14,07</t>
+          <t>11,06; 14,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,21; 23,16</t>
+          <t>6,86; 20,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,21; 9,94</t>
+          <t>8,26; 9,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 8,71</t>
+          <t>7,68; 8,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,95; 14,62</t>
+          <t>11,98; 14,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,76; 13,87</t>
+          <t>8,96; 13,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 8,95</t>
+          <t>7,49; 8,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,97; 14,12</t>
+          <t>11,92; 13,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,35; 14,7</t>
+          <t>9,41; 13,93</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,26</t>
+          <t>16,8</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,93</t>
+          <t>10,91</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,61</t>
+          <t>13,45</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,03</t>
+          <t>1,54; 3,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 3,77</t>
+          <t>2,62; 3,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,04; 10,76</t>
+          <t>7,96; 10,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,11; 20,99</t>
+          <t>10,91; 22,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,76</t>
+          <t>3,16; 4,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 5,26</t>
+          <t>4,24; 5,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,93; 13,52</t>
+          <t>9,91; 13,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,44; 14,53</t>
+          <t>8,58; 14,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 3,68</t>
+          <t>2,62; 3,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 4,45</t>
+          <t>3,69; 4,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,34; 11,55</t>
+          <t>9,43; 11,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,9; 15,67</t>
+          <t>10,47; 16,89</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,76</t>
+          <t>6,8</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,87</t>
+          <t>11,49</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,35</t>
+          <t>9,91</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,39</t>
+          <t>1,66; 2,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,65</t>
+          <t>5,14; 6,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,39</t>
+          <t>5,41; 8,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 7,95</t>
+          <t>5,35; 7,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 5,33</t>
+          <t>3,51; 5,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,66; 9,06</t>
+          <t>7,72; 9,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,38; 9,36</t>
+          <t>7,42; 9,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,22; 14,13</t>
+          <t>9,86; 13,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 3,92</t>
+          <t>2,8; 3,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,95</t>
+          <t>6,93; 7,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 8,68</t>
+          <t>6,88; 8,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,0; 12,5</t>
+          <t>8,51; 11,69</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>3,68</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>5,01</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,05</t>
+          <t>4,53; 8,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 6,02</t>
+          <t>4,19; 6,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 3,76</t>
+          <t>2,88; 3,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,64</t>
+          <t>2,84; 4,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,28; 10,55</t>
+          <t>7,37; 10,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 7,13</t>
+          <t>5,49; 7,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 4,83</t>
+          <t>4,15; 4,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,19</t>
+          <t>3,81; 6,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,62; 9,03</t>
+          <t>6,71; 9,03</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,48</t>
+          <t>5,27; 6,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 4,21</t>
+          <t>3,62; 4,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 4,84</t>
+          <t>3,47; 4,91</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12,2</t>
+          <t>12,03</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,19</t>
+          <t>12,22</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,2</t>
+          <t>12,13</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,35</t>
+          <t>1,67; 2,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 2,9</t>
+          <t>2,07; 2,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,3; 7,28</t>
+          <t>5,31; 7,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,37; 14,93</t>
+          <t>10,49; 14,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,81</t>
+          <t>4,8; 7,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,91; 5,06</t>
+          <t>3,9; 5,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,35; 10,29</t>
+          <t>7,27; 9,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,54; 14,3</t>
+          <t>10,71; 14,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,17</t>
+          <t>3,38; 5,26</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,24; 4,04</t>
+          <t>3,2; 4,04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,58; 8,37</t>
+          <t>6,63; 8,44</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,02; 13,9</t>
+          <t>10,98; 13,92</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12,32</t>
+          <t>12,85</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>19,78</t>
+          <t>17,15</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,64</t>
+          <t>16,08</t>
         </is>
       </c>
     </row>
@@ -1556,17 +1556,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,23</t>
+          <t>2,63; 4,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 3,47</t>
+          <t>2,82; 3,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,67; 11,34</t>
+          <t>8,8; 11,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1576,42 +1576,42 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,09; 5,49</t>
+          <t>4,1; 5,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,47; 5,23</t>
+          <t>4,49; 5,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,97; 13,11</t>
+          <t>10,93; 13,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,56; 22,83</t>
+          <t>10,65; 21,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,76</t>
+          <t>3,72; 4,84</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,84; 4,36</t>
+          <t>3,82; 4,38</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,41; 12,03</t>
+          <t>10,37; 12,03</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,4; 22,14</t>
+          <t>10,04; 21,33</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,07</t>
+          <t>4,11</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,68</t>
+          <t>5,85</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,06</t>
+          <t>5,17</t>
         </is>
       </c>
     </row>
@@ -1696,27 +1696,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,8; 7,61</t>
+          <t>5,85; 7,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,31; 6,37</t>
+          <t>5,35; 6,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,89; 4,53</t>
+          <t>3,9; 4,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,51</t>
+          <t>3,77; 4,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,46; 10,24</t>
+          <t>8,43; 10,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1726,32 +1726,32 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,4; 6,24</t>
+          <t>5,37; 6,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,3; 6,14</t>
+          <t>5,43; 6,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,51; 8,85</t>
+          <t>7,54; 8,9</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,5; 7,2</t>
+          <t>6,5; 7,16</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,86; 5,43</t>
+          <t>4,86; 5,46</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,78; 5,4</t>
+          <t>4,85; 5,49</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,23</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7,96</t>
+          <t>7,93</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>7,24</t>
         </is>
       </c>
     </row>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,65; 4,34</t>
+          <t>3,65; 4,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,68; 5,13</t>
+          <t>4,69; 5,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1851,47 +1851,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,48; 7,29</t>
+          <t>5,45; 7,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,87; 6,55</t>
+          <t>5,85; 6,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,55; 6,98</t>
+          <t>6,57; 6,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,59; 9,37</t>
+          <t>8,58; 9,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,41; 8,69</t>
+          <t>7,42; 8,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,11; 5,64</t>
+          <t>5,08; 5,59</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5,87; 6,19</t>
+          <t>5,88; 6,2</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,84; 8,44</t>
+          <t>7,86; 8,45</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,84</t>
+          <t>6,78; 7,74</t>
         </is>
       </c>
     </row>
